--- a/bids/Davidson, Ray/26_0803 Davidson, Ray PV ESS Bid.xlsx
+++ b/bids/Davidson, Ray/26_0803 Davidson, Ray PV ESS Bid.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph\Desktop\Code\MSSProposalAutomation\projects\3391894\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB3DF27-3B18-40B8-9B2D-8DF234717AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC3B2C2-D6F7-4BF9-A6DF-E5DCDF5F70E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="343" yWindow="3317" windowWidth="15514" windowHeight="10740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Info" sheetId="1" r:id="rId1"/>
